--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129310984</v>
+        <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562038</v>
+        <v>562005</v>
       </c>
       <c r="R9" t="n">
-        <v>7042536</v>
+        <v>7042560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129309285</v>
+        <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562005</v>
+        <v>562038</v>
       </c>
       <c r="R10" t="n">
-        <v>7042560</v>
+        <v>7042536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,45 +2304,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310631</v>
+        <v>129310847</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562130</v>
+        <v>562116</v>
       </c>
       <c r="R17" t="n">
-        <v>7042597</v>
+        <v>7042514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,7 +2388,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,10 +2415,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R18" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2485,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2495,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,32 +2522,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309112</v>
+        <v>129309443</v>
       </c>
       <c r="B19" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561993</v>
+        <v>562018</v>
       </c>
       <c r="R19" t="n">
-        <v>7042559</v>
+        <v>7042558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2592,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2602,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,49 +2629,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129310847</v>
+        <v>129309112</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562116</v>
+        <v>561993</v>
       </c>
       <c r="R20" t="n">
-        <v>7042514</v>
+        <v>7042559</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,38 +2736,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310484</v>
+        <v>129310206</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2776,10 +2775,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562079</v>
+        <v>562035</v>
       </c>
       <c r="R21" t="n">
-        <v>7042662</v>
+        <v>7042727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,7 +2810,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2821,12 +2820,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,10 +2847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2864,16 +2858,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2893,10 +2887,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R22" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,7 +2922,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2938,7 +2932,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,10 +2964,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2995,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3039,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,12 +3049,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,37 +3081,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310396</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562094</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3196,7 +3196,7 @@
         <v>129310210</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129310777</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3518,49 +3518,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310528</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562078</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042633</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3592,7 +3588,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3602,7 +3598,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,45 +3625,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310558</v>
+        <v>129310528</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562100</v>
+        <v>562078</v>
       </c>
       <c r="R29" t="n">
-        <v>7042638</v>
+        <v>7042633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,10 +3736,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310558</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562100</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,32 +3843,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310912</v>
+        <v>129310001</v>
       </c>
       <c r="B31" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562084</v>
+        <v>562049</v>
       </c>
       <c r="R31" t="n">
-        <v>7042525</v>
+        <v>7042649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,7 +3953,7 @@
         <v>129309746</v>
       </c>
       <c r="B32" t="n">
-        <v>79125</v>
+        <v>79127</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309754</v>
+        <v>129309127</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562081</v>
+        <v>561985</v>
       </c>
       <c r="R37" t="n">
-        <v>7042603</v>
+        <v>7042548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4596,10 +4596,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R38" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -1008,45 +1008,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310232</v>
+        <v>129310242</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562053</v>
+        <v>562061</v>
       </c>
       <c r="R5" t="n">
-        <v>7042723</v>
+        <v>7042718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,49 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310242</v>
+        <v>129310232</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562061</v>
+        <v>562053</v>
       </c>
       <c r="R6" t="n">
-        <v>7042718</v>
+        <v>7042723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2415,32 +2415,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310631</v>
+        <v>129309112</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562130</v>
+        <v>561993</v>
       </c>
       <c r="R18" t="n">
-        <v>7042597</v>
+        <v>7042559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R19" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,32 +2629,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309112</v>
+        <v>129309443</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561993</v>
+        <v>562018</v>
       </c>
       <c r="R20" t="n">
-        <v>7042559</v>
+        <v>7042558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,37 +2736,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310206</v>
+        <v>129310484</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2775,10 +2776,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562035</v>
+        <v>562079</v>
       </c>
       <c r="R21" t="n">
-        <v>7042727</v>
+        <v>7042662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,7 +2811,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2820,7 +2821,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2975,16 +2981,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2995,7 +3001,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3004,10 +3010,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R23" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,7 +3045,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3049,12 +3055,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,38 +3082,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310396</v>
+        <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562094</v>
+        <v>562035</v>
       </c>
       <c r="R24" t="n">
-        <v>7042667</v>
+        <v>7042727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,34 +3204,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R25" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,22 +3288,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,34 +3311,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R26" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,12 +3395,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3518,45 +3518,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310528</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562078</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3592,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,7 +3602,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,49 +3629,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310528</v>
+        <v>129310912</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562078</v>
+        <v>562084</v>
       </c>
       <c r="R29" t="n">
-        <v>7042633</v>
+        <v>7042525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>79127</v>
+        <v>92835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3961,21 +3961,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,22 +4045,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309661</v>
+        <v>129309746</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>79127</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,21 +4068,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562061</v>
+        <v>562063</v>
       </c>
       <c r="R33" t="n">
-        <v>7042576</v>
+        <v>7042591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4152,12 +4152,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B36" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,21 +4393,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R36" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4477,19 +4477,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R37" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4596,10 +4596,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R38" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4691,12 +4691,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129310242</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,49 +2304,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310847</v>
+        <v>129310631</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562116</v>
+        <v>562130</v>
       </c>
       <c r="R17" t="n">
-        <v>7042514</v>
+        <v>7042597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2388,7 +2384,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,32 +2411,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309112</v>
+        <v>129309443</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561993</v>
+        <v>562018</v>
       </c>
       <c r="R18" t="n">
-        <v>7042559</v>
+        <v>7042558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2495,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,45 +2518,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129310631</v>
+        <v>129310847</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562130</v>
+        <v>562116</v>
       </c>
       <c r="R19" t="n">
-        <v>7042597</v>
+        <v>7042514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,32 +2629,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R20" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,10 +2736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2747,16 +2747,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2767,7 +2767,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R21" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2821,12 +2821,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2853,7 +2848,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2884,7 +2879,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2893,10 +2888,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R22" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,7 +2923,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2938,12 +2933,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,10 +2965,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,16 +2976,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3010,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3055,7 +3050,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3085,7 +3085,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3518,49 +3518,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310528</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562078</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042633</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3592,7 +3588,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3602,7 +3598,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,45 +3625,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310912</v>
+        <v>129310528</v>
       </c>
       <c r="B29" t="n">
-        <v>92835</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562084</v>
+        <v>562078</v>
       </c>
       <c r="R29" t="n">
-        <v>7042525</v>
+        <v>7042633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3953,7 +3953,7 @@
         <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R36" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4489,10 +4489,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4500,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R37" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,22 +4584,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R38" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4691,12 +4691,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,49 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310242</v>
+        <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562061</v>
+        <v>562053</v>
       </c>
       <c r="R5" t="n">
-        <v>7042718</v>
+        <v>7042723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,45 +1115,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310232</v>
+        <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562053</v>
+        <v>562061</v>
       </c>
       <c r="R6" t="n">
-        <v>7042723</v>
+        <v>7042718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,45 +1872,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R13" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,49 +1983,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R14" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2110,14 +2110,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2521,7 +2517,7 @@
         <v>129310847</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2628,7 @@
         <v>129309112</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,38 +2732,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310396</v>
+        <v>129310206</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2776,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562094</v>
+        <v>562035</v>
       </c>
       <c r="R21" t="n">
-        <v>7042667</v>
+        <v>7042727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2811,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2821,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2848,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2859,16 +2854,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2879,7 +2874,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2888,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R22" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,7 +2918,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2933,12 +2928,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,7 +2955,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2996,7 +2986,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3030,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,12 +3040,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,37 +3072,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310662</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3121,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562130</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3156,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3166,7 +3157,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3204,34 +3200,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R25" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,57 +3284,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310210</v>
+        <v>129310333</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562045</v>
+        <v>562077</v>
       </c>
       <c r="R26" t="n">
-        <v>7042732</v>
+        <v>7042695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,61 +3395,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310333</v>
+        <v>129310777</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562077</v>
+        <v>562125</v>
       </c>
       <c r="R27" t="n">
-        <v>7042695</v>
+        <v>7042515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3491,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,45 +3514,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310528</v>
       </c>
       <c r="B28" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562078</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,49 +3625,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310528</v>
+        <v>129310912</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>92822</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562078</v>
+        <v>562084</v>
       </c>
       <c r="R29" t="n">
-        <v>7042633</v>
+        <v>7042525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3699,7 +3695,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3709,7 +3705,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,7 +3732,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3771,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R30" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3806,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3816,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3843,7 +3839,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310001</v>
+        <v>129310558</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3878,10 +3874,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562049</v>
+        <v>562100</v>
       </c>
       <c r="R31" t="n">
-        <v>7042649</v>
+        <v>7042638</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3913,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3923,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,7 +3949,7 @@
         <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4057,45 +4053,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309746</v>
+        <v>129310811</v>
       </c>
       <c r="B33" t="n">
-        <v>79127</v>
+        <v>98705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562063</v>
+        <v>562122</v>
       </c>
       <c r="R33" t="n">
-        <v>7042591</v>
+        <v>7042513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,61 +4152,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>79127</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R34" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4248,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4263,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4278,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4382,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4393,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4417,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R36" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4462,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4477,22 +4473,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B37" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4500,21 +4496,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4524,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R37" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4569,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4584,19 +4580,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4631,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R38" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4666,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4676,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129310389</v>
+        <v>129309880</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562065</v>
+        <v>562069</v>
       </c>
       <c r="R2" t="n">
-        <v>7042680</v>
+        <v>7042614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310680</v>
+        <v>129310389</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562140</v>
+        <v>562065</v>
       </c>
       <c r="R3" t="n">
-        <v>7042590</v>
+        <v>7042680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129309880</v>
+        <v>129310680</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562069</v>
+        <v>562140</v>
       </c>
       <c r="R4" t="n">
-        <v>7042614</v>
+        <v>7042590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,49 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R13" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,45 +1979,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R14" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2514,49 +2514,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129310847</v>
+        <v>129309112</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>92822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562116</v>
+        <v>561993</v>
       </c>
       <c r="R19" t="n">
-        <v>7042514</v>
+        <v>7042559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,45 +2621,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309112</v>
+        <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561993</v>
+        <v>562116</v>
       </c>
       <c r="R20" t="n">
-        <v>7042559</v>
+        <v>7042514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,37 +2732,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310206</v>
+        <v>129310484</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2771,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562035</v>
+        <v>562079</v>
       </c>
       <c r="R21" t="n">
-        <v>7042727</v>
+        <v>7042662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2817,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,16 +2860,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2883,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R22" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2928,7 +2934,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,16 +2977,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2986,7 +2997,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2995,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R23" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3040,12 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,38 +3078,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310662</v>
+        <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3112,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562130</v>
+        <v>562035</v>
       </c>
       <c r="R24" t="n">
-        <v>7042598</v>
+        <v>7042727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,12 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,7 +3299,7 @@
         <v>129310333</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3514,49 +3514,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310528</v>
+        <v>129310558</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562078</v>
+        <v>562100</v>
       </c>
       <c r="R28" t="n">
-        <v>7042633</v>
+        <v>7042638</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,32 +3621,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310912</v>
+        <v>129310001</v>
       </c>
       <c r="B29" t="n">
-        <v>92822</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3660,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562084</v>
+        <v>562049</v>
       </c>
       <c r="R29" t="n">
-        <v>7042525</v>
+        <v>7042649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3705,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3767,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,45 +3835,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310558</v>
+        <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562100</v>
+        <v>562078</v>
       </c>
       <c r="R31" t="n">
-        <v>7042638</v>
+        <v>7042633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,45 +3946,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309661</v>
+        <v>129310811</v>
       </c>
       <c r="B32" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562061</v>
+        <v>562122</v>
       </c>
       <c r="R32" t="n">
-        <v>7042576</v>
+        <v>7042513</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4020,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4030,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,49 +4057,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B33" t="n">
-        <v>98705</v>
+        <v>79127</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R33" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,22 +4152,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B34" t="n">
-        <v>79127</v>
+        <v>92822</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R34" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R36" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,19 +4473,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R37" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R38" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309880</v>
+        <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562069</v>
+        <v>562065</v>
       </c>
       <c r="R2" t="n">
-        <v>7042614</v>
+        <v>7042680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310389</v>
+        <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562065</v>
+        <v>562140</v>
       </c>
       <c r="R3" t="n">
-        <v>7042680</v>
+        <v>7042590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129310680</v>
+        <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562140</v>
+        <v>562069</v>
       </c>
       <c r="R4" t="n">
-        <v>7042590</v>
+        <v>7042614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,45 +1872,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R13" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,49 +1983,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R14" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310631</v>
+        <v>129309112</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562130</v>
+        <v>561993</v>
       </c>
       <c r="R17" t="n">
-        <v>7042597</v>
+        <v>7042559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R18" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2514,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309112</v>
+        <v>129309443</v>
       </c>
       <c r="B19" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561993</v>
+        <v>562018</v>
       </c>
       <c r="R19" t="n">
-        <v>7042559</v>
+        <v>7042558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2763,7 +2763,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R21" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,12 +2817,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,7 +2844,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2880,7 +2875,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2889,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R22" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,7 +2919,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,12 +2929,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,16 +2972,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3006,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,7 +3036,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3051,7 +3046,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R25" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,61 +3284,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R26" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,57 +3391,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310777</v>
+        <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562125</v>
+        <v>562077</v>
       </c>
       <c r="R27" t="n">
-        <v>7042515</v>
+        <v>7042695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310558</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562100</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042638</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,7 +3624,7 @@
         <v>129310001</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B30" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R30" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,7 +3838,7 @@
         <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,49 +3946,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>79129</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R32" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4020,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4030,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,57 +4041,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309746</v>
+        <v>129310811</v>
       </c>
       <c r="B33" t="n">
-        <v>79127</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562063</v>
+        <v>562122</v>
       </c>
       <c r="R33" t="n">
-        <v>7042591</v>
+        <v>7042513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,12 +4152,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4167,7 +4167,7 @@
         <v>129309661</v>
       </c>
       <c r="B34" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309127</v>
+        <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561985</v>
+        <v>562088</v>
       </c>
       <c r="R36" t="n">
-        <v>7042548</v>
+        <v>7042660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,22 +4473,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309754</v>
+        <v>129309127</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562081</v>
+        <v>561985</v>
       </c>
       <c r="R37" t="n">
-        <v>7042603</v>
+        <v>7042548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310114</v>
+        <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562088</v>
+        <v>562081</v>
       </c>
       <c r="R38" t="n">
-        <v>7042660</v>
+        <v>7042603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -1872,49 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R13" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,45 +1979,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R14" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310001</v>
       </c>
       <c r="B28" t="n">
-        <v>92825</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562049</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042649</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3621,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310001</v>
+        <v>129310558</v>
       </c>
       <c r="B29" t="n">
         <v>79043</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562049</v>
+        <v>562100</v>
       </c>
       <c r="R29" t="n">
-        <v>7042649</v>
+        <v>7042638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310558</v>
+        <v>129310912</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>92825</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562100</v>
+        <v>562084</v>
       </c>
       <c r="R30" t="n">
-        <v>7042638</v>
+        <v>7042525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4053,49 +4053,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129310811</v>
+        <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562122</v>
+        <v>562061</v>
       </c>
       <c r="R33" t="n">
-        <v>7042513</v>
+        <v>7042576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4123,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4133,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4164,45 +4160,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309661</v>
+        <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>92825</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562061</v>
+        <v>562122</v>
       </c>
       <c r="R34" t="n">
-        <v>7042576</v>
+        <v>7042513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,45 +1872,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R13" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,49 +1983,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R14" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R17" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310631</v>
+        <v>129309443</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562130</v>
+        <v>562018</v>
       </c>
       <c r="R18" t="n">
-        <v>7042597</v>
+        <v>7042558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2514,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R19" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R21" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2817,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310396</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,16 +2977,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3001,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562094</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3046,12 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,45 +3189,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310777</v>
+        <v>129310333</v>
       </c>
       <c r="B25" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562125</v>
+        <v>562077</v>
       </c>
       <c r="R25" t="n">
-        <v>7042515</v>
+        <v>7042695</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,34 +3311,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R26" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,61 +3395,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R27" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,44 +3502,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3624,7 +3624,7 @@
         <v>129310558</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310912</v>
+        <v>129310001</v>
       </c>
       <c r="B30" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562084</v>
+        <v>562049</v>
       </c>
       <c r="R30" t="n">
-        <v>7042525</v>
+        <v>7042649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,7 +3838,7 @@
         <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>79129</v>
+        <v>92827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,22 +4041,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309661</v>
+        <v>129309746</v>
       </c>
       <c r="B33" t="n">
-        <v>92825</v>
+        <v>79130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562061</v>
+        <v>562063</v>
       </c>
       <c r="R33" t="n">
-        <v>7042576</v>
+        <v>7042591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,12 +4148,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
         <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B36" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R36" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,22 +4473,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R37" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R38" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,49 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R13" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,45 +1979,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R14" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,45 +2300,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310631</v>
+        <v>129310847</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562130</v>
+        <v>562116</v>
       </c>
       <c r="R17" t="n">
-        <v>7042597</v>
+        <v>7042514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2384,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2411,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R18" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2518,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R19" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2588,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2598,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,49 +2625,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129310847</v>
+        <v>129309443</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562116</v>
+        <v>562018</v>
       </c>
       <c r="R20" t="n">
-        <v>7042514</v>
+        <v>7042558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310662</v>
+        <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562130</v>
+        <v>562094</v>
       </c>
       <c r="R21" t="n">
-        <v>7042598</v>
+        <v>7042667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,12 +2817,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,16 +2972,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3006,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,7 +3036,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3051,7 +3046,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>129310333</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129310777</v>
       </c>
       <c r="B26" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B28" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3621,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R29" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,7 +3838,7 @@
         <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,45 +4053,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309746</v>
+        <v>129310811</v>
       </c>
       <c r="B33" t="n">
-        <v>79130</v>
+        <v>98716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562063</v>
+        <v>562122</v>
       </c>
       <c r="R33" t="n">
-        <v>7042591</v>
+        <v>7042513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4123,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4133,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,61 +4152,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>79130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R34" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309127</v>
+        <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561985</v>
+        <v>562088</v>
       </c>
       <c r="R36" t="n">
-        <v>7042548</v>
+        <v>7042660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,19 +4473,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309754</v>
+        <v>129309127</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562081</v>
+        <v>561985</v>
       </c>
       <c r="R37" t="n">
-        <v>7042603</v>
+        <v>7042548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310114</v>
+        <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562088</v>
+        <v>562081</v>
       </c>
       <c r="R38" t="n">
-        <v>7042660</v>
+        <v>7042603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,45 +1008,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310232</v>
+        <v>129310242</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562053</v>
+        <v>562061</v>
       </c>
       <c r="R5" t="n">
-        <v>7042723</v>
+        <v>7042718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,49 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310242</v>
+        <v>129310232</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562061</v>
+        <v>562053</v>
       </c>
       <c r="R6" t="n">
-        <v>7042718</v>
+        <v>7042723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>129310847</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,32 +2411,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B18" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R18" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129310631</v>
+        <v>129309443</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562130</v>
+        <v>562018</v>
       </c>
       <c r="R19" t="n">
-        <v>7042597</v>
+        <v>7042558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,32 +2625,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R20" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310396</v>
+        <v>129310484</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2763,7 +2763,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562094</v>
+        <v>562079</v>
       </c>
       <c r="R21" t="n">
-        <v>7042667</v>
+        <v>7042662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2817,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,7 +2849,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310484</v>
+        <v>129310662</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2875,7 +2880,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2884,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562079</v>
+        <v>562130</v>
       </c>
       <c r="R22" t="n">
-        <v>7042662</v>
+        <v>7042598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2929,12 +2934,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,38 +2966,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310206</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3001,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562035</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042727</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3046,12 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,37 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310396</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562094</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,49 +3189,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310333</v>
+        <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562077</v>
+        <v>562125</v>
       </c>
       <c r="R25" t="n">
-        <v>7042695</v>
+        <v>7042515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,34 +3307,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R26" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,57 +3391,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310210</v>
+        <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562045</v>
+        <v>562077</v>
       </c>
       <c r="R27" t="n">
-        <v>7042732</v>
+        <v>7042695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3731,7 +3731,7 @@
         <v>129310912</v>
       </c>
       <c r="B30" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309661</v>
+        <v>129309746</v>
       </c>
       <c r="B32" t="n">
-        <v>92831</v>
+        <v>79130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562061</v>
+        <v>562063</v>
       </c>
       <c r="R32" t="n">
-        <v>7042576</v>
+        <v>7042591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,61 +4041,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129310811</v>
+        <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>98716</v>
+        <v>92832</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562122</v>
+        <v>562061</v>
       </c>
       <c r="R33" t="n">
-        <v>7042513</v>
+        <v>7042576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4123,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4133,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4164,45 +4160,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309746</v>
+        <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>79130</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562063</v>
+        <v>562122</v>
       </c>
       <c r="R34" t="n">
-        <v>7042591</v>
+        <v>7042513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -1008,49 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310242</v>
+        <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562061</v>
+        <v>562053</v>
       </c>
       <c r="R5" t="n">
-        <v>7042718</v>
+        <v>7042723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,45 +1115,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310232</v>
+        <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562053</v>
+        <v>562061</v>
       </c>
       <c r="R6" t="n">
-        <v>7042723</v>
+        <v>7042718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2300,49 +2300,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310847</v>
+        <v>129309112</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562116</v>
+        <v>561993</v>
       </c>
       <c r="R17" t="n">
-        <v>7042514</v>
+        <v>7042559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2625,45 +2621,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309112</v>
+        <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561993</v>
+        <v>562116</v>
       </c>
       <c r="R20" t="n">
-        <v>7042559</v>
+        <v>7042514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2966,37 +2966,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310206</v>
+        <v>129310396</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562035</v>
+        <v>562094</v>
       </c>
       <c r="R23" t="n">
-        <v>7042727</v>
+        <v>7042667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3078,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310396</v>
+        <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562094</v>
+        <v>562035</v>
       </c>
       <c r="R24" t="n">
-        <v>7042667</v>
+        <v>7042727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310558</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562100</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042638</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B30" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R30" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>79130</v>
+        <v>92832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,22 +4041,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309661</v>
+        <v>129309746</v>
       </c>
       <c r="B33" t="n">
-        <v>92832</v>
+        <v>79130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562061</v>
+        <v>562063</v>
       </c>
       <c r="R33" t="n">
-        <v>7042576</v>
+        <v>7042591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,12 +4148,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2763,7 +2763,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R21" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,12 +2817,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,7 +2844,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B22" t="n">
         <v>57727</v>
@@ -2880,7 +2875,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2889,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R22" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,7 +2919,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,12 +2929,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,16 +2972,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3006,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,7 +3036,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3051,7 +3046,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,45 +3296,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310210</v>
+        <v>129310333</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562045</v>
+        <v>562077</v>
       </c>
       <c r="R26" t="n">
-        <v>7042732</v>
+        <v>7042695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,61 +3395,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R27" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,57 +3502,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310528</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562078</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3588,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3598,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,32 +3625,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3660,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R29" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3695,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3705,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,7 +3732,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3763,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R30" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,49 +3839,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310528</v>
+        <v>129310558</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562078</v>
+        <v>562100</v>
       </c>
       <c r="R31" t="n">
-        <v>7042633</v>
+        <v>7042638</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R17" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310631</v>
+        <v>129309443</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562130</v>
+        <v>562018</v>
       </c>
       <c r="R18" t="n">
-        <v>7042597</v>
+        <v>7042558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2514,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R19" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,38 +2732,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310396</v>
+        <v>129310206</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2772,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562094</v>
+        <v>562035</v>
       </c>
       <c r="R21" t="n">
-        <v>7042667</v>
+        <v>7042727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310484</v>
+        <v>129310396</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,16 +2854,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2875,7 +2874,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2884,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562079</v>
+        <v>562094</v>
       </c>
       <c r="R22" t="n">
-        <v>7042662</v>
+        <v>7042667</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2918,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2929,12 +2928,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,7 +2955,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2992,7 +2986,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3001,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +3030,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3046,12 +3040,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,37 +3072,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310662</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562130</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3157,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R25" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,61 +3284,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310333</v>
+        <v>129310777</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562077</v>
+        <v>562125</v>
       </c>
       <c r="R26" t="n">
-        <v>7042695</v>
+        <v>7042515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,45 +3403,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310210</v>
+        <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562045</v>
+        <v>562077</v>
       </c>
       <c r="R27" t="n">
-        <v>7042732</v>
+        <v>7042695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,61 +3502,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310528</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562078</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042633</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,45 +3621,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310912</v>
+        <v>129310528</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562084</v>
+        <v>562078</v>
       </c>
       <c r="R29" t="n">
-        <v>7042525</v>
+        <v>7042633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,7 +3732,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310558</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562100</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,7 +3839,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R31" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309661</v>
+        <v>129309746</v>
       </c>
       <c r="B32" t="n">
-        <v>92832</v>
+        <v>79130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562061</v>
+        <v>562063</v>
       </c>
       <c r="R32" t="n">
-        <v>7042576</v>
+        <v>7042591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,22 +4041,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>79130</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R33" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,12 +4148,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
         <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -2732,37 +2732,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310206</v>
+        <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2771,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562035</v>
+        <v>562094</v>
       </c>
       <c r="R21" t="n">
-        <v>7042727</v>
+        <v>7042667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2817,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2844,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310396</v>
+        <v>129310484</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,16 +2855,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2874,7 +2875,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2883,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562094</v>
+        <v>562079</v>
       </c>
       <c r="R22" t="n">
-        <v>7042667</v>
+        <v>7042662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2919,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2928,7 +2929,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2961,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310484</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2986,7 +2992,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2995,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562079</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042662</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3036,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3040,12 +3046,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,38 +3078,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310662</v>
+        <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3112,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562130</v>
+        <v>562035</v>
       </c>
       <c r="R24" t="n">
-        <v>7042598</v>
+        <v>7042727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,12 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,49 +3621,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310528</v>
+        <v>129310001</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562078</v>
+        <v>562049</v>
       </c>
       <c r="R29" t="n">
-        <v>7042633</v>
+        <v>7042649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3705,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,45 +3728,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310558</v>
+        <v>129310528</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562100</v>
+        <v>562078</v>
       </c>
       <c r="R30" t="n">
-        <v>7042638</v>
+        <v>7042633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,32 +3839,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R31" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>79130</v>
+        <v>92835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,57 +4041,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309661</v>
+        <v>129310811</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562061</v>
+        <v>562122</v>
       </c>
       <c r="R33" t="n">
-        <v>7042576</v>
+        <v>7042513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4123,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4133,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4160,49 +4164,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>79130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R34" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129310389</v>
+        <v>129309880</v>
       </c>
       <c r="B2" t="n">
         <v>98727</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562065</v>
+        <v>562069</v>
       </c>
       <c r="R2" t="n">
-        <v>7042680</v>
+        <v>7042614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310680</v>
+        <v>129310389</v>
       </c>
       <c r="B3" t="n">
         <v>98727</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562140</v>
+        <v>562065</v>
       </c>
       <c r="R3" t="n">
-        <v>7042590</v>
+        <v>7042680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129309880</v>
+        <v>129310680</v>
       </c>
       <c r="B4" t="n">
         <v>98727</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562069</v>
+        <v>562140</v>
       </c>
       <c r="R4" t="n">
-        <v>7042614</v>
+        <v>7042590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310631</v>
+        <v>129309112</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562130</v>
+        <v>561993</v>
       </c>
       <c r="R17" t="n">
-        <v>7042597</v>
+        <v>7042559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R18" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2514,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309112</v>
+        <v>129309443</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561993</v>
+        <v>562018</v>
       </c>
       <c r="R19" t="n">
-        <v>7042559</v>
+        <v>7042558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310558</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562100</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042638</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3621,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310001</v>
+        <v>129310558</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562049</v>
+        <v>562100</v>
       </c>
       <c r="R29" t="n">
-        <v>7042649</v>
+        <v>7042638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,49 +3728,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310528</v>
+        <v>129310001</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562078</v>
+        <v>562049</v>
       </c>
       <c r="R30" t="n">
-        <v>7042633</v>
+        <v>7042649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,45 +3835,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310912</v>
+        <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562084</v>
+        <v>562078</v>
       </c>
       <c r="R31" t="n">
-        <v>7042525</v>
+        <v>7042633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,45 +3946,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309661</v>
+        <v>129310811</v>
       </c>
       <c r="B32" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562061</v>
+        <v>562122</v>
       </c>
       <c r="R32" t="n">
-        <v>7042576</v>
+        <v>7042513</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4020,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4030,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,49 +4057,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>79130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R33" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,22 +4152,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B34" t="n">
-        <v>79130</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R34" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -1872,45 +1872,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R13" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,49 +1983,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R14" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2407,45 +2407,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310631</v>
+        <v>129310847</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562130</v>
+        <v>562116</v>
       </c>
       <c r="R18" t="n">
-        <v>7042597</v>
+        <v>7042514</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,7 +2518,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2549,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R19" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2588,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2598,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,49 +2625,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129310847</v>
+        <v>129309443</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562116</v>
+        <v>562018</v>
       </c>
       <c r="R20" t="n">
-        <v>7042514</v>
+        <v>7042558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R25" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,22 +3284,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,34 +3307,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R26" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,12 +3391,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3514,32 +3514,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3621,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R29" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,49 +3946,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129310811</v>
+        <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>92835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562122</v>
+        <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042513</v>
+        <v>7042576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4020,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4030,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4164,45 +4160,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309661</v>
+        <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562061</v>
+        <v>562122</v>
       </c>
       <c r="R34" t="n">
-        <v>7042576</v>
+        <v>7042513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R36" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,19 +4473,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R37" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R38" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309880</v>
+        <v>129310389</v>
       </c>
       <c r="B2" t="n">
         <v>98727</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562069</v>
+        <v>562065</v>
       </c>
       <c r="R2" t="n">
-        <v>7042614</v>
+        <v>7042680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310389</v>
+        <v>129310680</v>
       </c>
       <c r="B3" t="n">
         <v>98727</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562065</v>
+        <v>562140</v>
       </c>
       <c r="R3" t="n">
-        <v>7042680</v>
+        <v>7042590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129310680</v>
+        <v>129309880</v>
       </c>
       <c r="B4" t="n">
         <v>98727</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562140</v>
+        <v>562069</v>
       </c>
       <c r="R4" t="n">
-        <v>7042590</v>
+        <v>7042614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R17" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,49 +2407,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310847</v>
+        <v>129309443</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562116</v>
+        <v>562018</v>
       </c>
       <c r="R18" t="n">
-        <v>7042514</v>
+        <v>7042558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,32 +2514,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129310631</v>
+        <v>129309112</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2553,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562130</v>
+        <v>561993</v>
       </c>
       <c r="R19" t="n">
-        <v>7042597</v>
+        <v>7042559</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,45 +2621,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309443</v>
+        <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562018</v>
+        <v>562116</v>
       </c>
       <c r="R20" t="n">
-        <v>7042558</v>
+        <v>7042514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,38 +2844,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310484</v>
+        <v>129310206</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2884,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562079</v>
+        <v>562035</v>
       </c>
       <c r="R22" t="n">
-        <v>7042662</v>
+        <v>7042727</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2918,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2929,12 +2928,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,7 +2955,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310484</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2992,7 +2986,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3001,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562079</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +3030,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3046,12 +3040,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,37 +3072,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310662</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562130</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042598</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3157,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,45 +3189,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310777</v>
+        <v>129310333</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562125</v>
+        <v>562077</v>
       </c>
       <c r="R25" t="n">
-        <v>7042515</v>
+        <v>7042695</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,34 +3311,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R26" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,61 +3395,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R27" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,44 +3502,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310558</v>
+        <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562100</v>
+        <v>562084</v>
       </c>
       <c r="R28" t="n">
-        <v>7042638</v>
+        <v>7042525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3621,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310001</v>
+        <v>129310558</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562049</v>
+        <v>562100</v>
       </c>
       <c r="R29" t="n">
-        <v>7042649</v>
+        <v>7042638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310912</v>
+        <v>129310001</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562084</v>
+        <v>562049</v>
       </c>
       <c r="R30" t="n">
-        <v>7042525</v>
+        <v>7042649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309127</v>
+        <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561985</v>
+        <v>562088</v>
       </c>
       <c r="R36" t="n">
-        <v>7042548</v>
+        <v>7042660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,19 +4473,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309754</v>
+        <v>129309127</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562081</v>
+        <v>561985</v>
       </c>
       <c r="R37" t="n">
-        <v>7042603</v>
+        <v>7042548</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310114</v>
+        <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562088</v>
+        <v>562081</v>
       </c>
       <c r="R38" t="n">
-        <v>7042660</v>
+        <v>7042603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129310389</v>
+        <v>129309880</v>
       </c>
       <c r="B2" t="n">
         <v>98727</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562065</v>
+        <v>562069</v>
       </c>
       <c r="R2" t="n">
-        <v>7042680</v>
+        <v>7042614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310680</v>
+        <v>129310389</v>
       </c>
       <c r="B3" t="n">
         <v>98727</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562140</v>
+        <v>562065</v>
       </c>
       <c r="R3" t="n">
-        <v>7042590</v>
+        <v>7042680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,19 +885,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129309880</v>
+        <v>129310680</v>
       </c>
       <c r="B4" t="n">
         <v>98727</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562069</v>
+        <v>562140</v>
       </c>
       <c r="R4" t="n">
-        <v>7042614</v>
+        <v>7042590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,45 +1008,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310232</v>
+        <v>129310242</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562053</v>
+        <v>562061</v>
       </c>
       <c r="R5" t="n">
-        <v>7042723</v>
+        <v>7042718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1092,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,49 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310242</v>
+        <v>129310232</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562061</v>
+        <v>562053</v>
       </c>
       <c r="R6" t="n">
-        <v>7042718</v>
+        <v>7042723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2300,45 +2300,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310631</v>
+        <v>129310847</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562130</v>
+        <v>562116</v>
       </c>
       <c r="R17" t="n">
-        <v>7042597</v>
+        <v>7042514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2384,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2411,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2446,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R18" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2481,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2491,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,32 +2518,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2553,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R19" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2588,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2598,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,49 +2625,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129310847</v>
+        <v>129309443</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562116</v>
+        <v>562018</v>
       </c>
       <c r="R20" t="n">
-        <v>7042514</v>
+        <v>7042558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,37 +2844,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310206</v>
+        <v>129310484</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2883,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562035</v>
+        <v>562079</v>
       </c>
       <c r="R22" t="n">
-        <v>7042727</v>
+        <v>7042662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2919,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2928,7 +2929,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,7 +2961,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310484</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
         <v>57727</v>
@@ -2986,7 +2992,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2995,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562079</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042662</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3036,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3040,12 +3046,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,38 +3078,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310662</v>
+        <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3112,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562130</v>
+        <v>562035</v>
       </c>
       <c r="R24" t="n">
-        <v>7042598</v>
+        <v>7042727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,12 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,49 +3189,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310333</v>
+        <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562077</v>
+        <v>562125</v>
       </c>
       <c r="R25" t="n">
-        <v>7042695</v>
+        <v>7042515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,34 +3307,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R26" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,57 +3391,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310210</v>
+        <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562045</v>
+        <v>562077</v>
       </c>
       <c r="R27" t="n">
-        <v>7042732</v>
+        <v>7042695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3946,45 +3946,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309661</v>
+        <v>129310811</v>
       </c>
       <c r="B32" t="n">
-        <v>92835</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562061</v>
+        <v>562122</v>
       </c>
       <c r="R32" t="n">
-        <v>7042576</v>
+        <v>7042513</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4020,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4030,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,10 +4057,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>79130</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,21 +4068,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4092,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R33" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,61 +4152,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>79130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R34" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309880</v>
+        <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562069</v>
+        <v>562065</v>
       </c>
       <c r="R2" t="n">
-        <v>7042614</v>
+        <v>7042680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310389</v>
+        <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562065</v>
+        <v>562140</v>
       </c>
       <c r="R3" t="n">
-        <v>7042680</v>
+        <v>7042590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129310680</v>
+        <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562140</v>
+        <v>562069</v>
       </c>
       <c r="R4" t="n">
-        <v>7042590</v>
+        <v>7042614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>129310242</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129310232</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,49 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R13" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,45 +1979,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R14" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,49 +2300,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129310847</v>
+        <v>129309112</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562116</v>
+        <v>561993</v>
       </c>
       <c r="R17" t="n">
-        <v>7042514</v>
+        <v>7042559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2384,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2411,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R18" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2481,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2491,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129310631</v>
+        <v>129309443</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2553,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562130</v>
+        <v>562018</v>
       </c>
       <c r="R19" t="n">
-        <v>7042597</v>
+        <v>7042558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2598,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,45 +2621,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129309443</v>
+        <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562018</v>
+        <v>562116</v>
       </c>
       <c r="R20" t="n">
-        <v>7042558</v>
+        <v>7042514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,7 +2735,7 @@
         <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>129310484</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,45 +3189,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310777</v>
+        <v>129310333</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562125</v>
+        <v>562077</v>
       </c>
       <c r="R25" t="n">
-        <v>7042515</v>
+        <v>7042695</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,34 +3311,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R26" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,61 +3395,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R27" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
         <v>129310912</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>129310558</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>129310001</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129310811</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129309746</v>
       </c>
       <c r="B34" t="n">
-        <v>79130</v>
+        <v>79156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>129309127</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -3946,49 +3946,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>79156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R32" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4020,7 +4016,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4030,7 +4026,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4045,12 +4041,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4164,45 +4160,49 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309746</v>
+        <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>79156</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562063</v>
+        <v>562122</v>
       </c>
       <c r="R34" t="n">
-        <v>7042591</v>
+        <v>7042513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129310389</v>
+        <v>129309880</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562065</v>
+        <v>562069</v>
       </c>
       <c r="R2" t="n">
-        <v>7042680</v>
+        <v>7042614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310680</v>
+        <v>129310389</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562140</v>
+        <v>562065</v>
       </c>
       <c r="R3" t="n">
-        <v>7042590</v>
+        <v>7042680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129309880</v>
+        <v>129310680</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562069</v>
+        <v>562140</v>
       </c>
       <c r="R4" t="n">
-        <v>7042614</v>
+        <v>7042590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,49 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310242</v>
+        <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562061</v>
+        <v>562053</v>
       </c>
       <c r="R5" t="n">
-        <v>7042718</v>
+        <v>7042723</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1092,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,45 +1115,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310232</v>
+        <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562053</v>
+        <v>562061</v>
       </c>
       <c r="R6" t="n">
-        <v>7042723</v>
+        <v>7042718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,45 +1872,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R13" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,49 +1983,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R14" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129309112</v>
+        <v>129309443</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561993</v>
+        <v>562018</v>
       </c>
       <c r="R17" t="n">
-        <v>7042559</v>
+        <v>7042558</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310631</v>
+        <v>129309112</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562130</v>
+        <v>561993</v>
       </c>
       <c r="R18" t="n">
-        <v>7042597</v>
+        <v>7042559</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R19" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310396</v>
+        <v>129310484</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2763,7 +2763,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562094</v>
+        <v>562079</v>
       </c>
       <c r="R21" t="n">
-        <v>7042667</v>
+        <v>7042662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2817,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310484</v>
+        <v>129310662</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2875,7 +2880,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2884,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562079</v>
+        <v>562130</v>
       </c>
       <c r="R22" t="n">
-        <v>7042662</v>
+        <v>7042598</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2929,12 +2934,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310396</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,16 +2977,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3001,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562094</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3046,12 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,49 +3189,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R25" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3263,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3273,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,57 +3284,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310777</v>
+        <v>129310333</v>
       </c>
       <c r="B26" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562125</v>
+        <v>562077</v>
       </c>
       <c r="R26" t="n">
-        <v>7042515</v>
+        <v>7042695</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,34 +3418,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R27" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,44 +3502,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B28" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R28" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R29" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3728,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>92869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,7 +3838,7 @@
         <v>129310528</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>129309746</v>
       </c>
       <c r="B32" t="n">
-        <v>79156</v>
+        <v>79161</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>129309661</v>
       </c>
       <c r="B33" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>129309127</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309880</v>
+        <v>129310389</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562069</v>
+        <v>562065</v>
       </c>
       <c r="R2" t="n">
-        <v>7042614</v>
+        <v>7042680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310389</v>
+        <v>129310680</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562065</v>
+        <v>562140</v>
       </c>
       <c r="R3" t="n">
-        <v>7042680</v>
+        <v>7042590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129310680</v>
+        <v>129309880</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562140</v>
+        <v>562069</v>
       </c>
       <c r="R4" t="n">
-        <v>7042590</v>
+        <v>7042614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,49 +1872,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310043</v>
+        <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562044</v>
+        <v>562072</v>
       </c>
       <c r="R13" t="n">
-        <v>7042672</v>
+        <v>7042648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,45 +1979,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310513</v>
+        <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562072</v>
+        <v>562044</v>
       </c>
       <c r="R14" t="n">
-        <v>7042648</v>
+        <v>7042672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129309443</v>
+        <v>129309112</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562018</v>
+        <v>561993</v>
       </c>
       <c r="R17" t="n">
-        <v>7042558</v>
+        <v>7042559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129309112</v>
+        <v>129310631</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561993</v>
+        <v>562130</v>
       </c>
       <c r="R18" t="n">
-        <v>7042559</v>
+        <v>7042597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129310631</v>
+        <v>129309443</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562130</v>
+        <v>562018</v>
       </c>
       <c r="R19" t="n">
-        <v>7042597</v>
+        <v>7042558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2624,7 @@
         <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,38 +2732,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310484</v>
+        <v>129310206</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2772,10 +2771,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562079</v>
+        <v>562035</v>
       </c>
       <c r="R21" t="n">
-        <v>7042662</v>
+        <v>7042727</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2806,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,12 +2816,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,10 +2843,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310662</v>
+        <v>129310396</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,16 +2854,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2889,10 +2883,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562130</v>
+        <v>562094</v>
       </c>
       <c r="R22" t="n">
-        <v>7042598</v>
+        <v>7042667</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,7 +2918,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2934,12 +2928,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,10 +2955,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,16 +2966,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3006,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,7 +3030,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3051,7 +3040,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,37 +3072,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310484</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562079</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,7 +3147,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3157,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310210</v>
+        <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,34 +3200,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562045</v>
+        <v>562125</v>
       </c>
       <c r="R25" t="n">
-        <v>7042732</v>
+        <v>7042515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,12 +3284,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
         <v>129310333</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310777</v>
+        <v>129310210</v>
       </c>
       <c r="B27" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,34 +3418,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562125</v>
+        <v>562045</v>
       </c>
       <c r="R27" t="n">
-        <v>7042515</v>
+        <v>7042732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,57 +3502,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310558</v>
+        <v>129310528</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562100</v>
+        <v>562078</v>
       </c>
       <c r="R28" t="n">
-        <v>7042638</v>
+        <v>7042633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3588,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3598,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,32 +3625,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3660,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R29" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3695,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3705,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3732,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B30" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R30" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,49 +3839,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310528</v>
+        <v>129310001</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562078</v>
+        <v>562049</v>
       </c>
       <c r="R31" t="n">
-        <v>7042633</v>
+        <v>7042649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,10 +3946,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309746</v>
+        <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>79161</v>
+        <v>92870</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562063</v>
+        <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042591</v>
+        <v>7042576</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,22 +4041,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309661</v>
+        <v>129309746</v>
       </c>
       <c r="B33" t="n">
-        <v>92869</v>
+        <v>79162</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4064,21 +4064,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562061</v>
+        <v>562063</v>
       </c>
       <c r="R33" t="n">
-        <v>7042576</v>
+        <v>7042591</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,12 +4148,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
         <v>129310811</v>
       </c>
       <c r="B34" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129310114</v>
       </c>
       <c r="B36" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>129309127</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>129309754</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -2732,37 +2732,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310206</v>
+        <v>129310662</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2771,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562035</v>
+        <v>562130</v>
       </c>
       <c r="R21" t="n">
-        <v>7042727</v>
+        <v>7042598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2816,7 +2817,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310396</v>
+        <v>129310484</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,16 +2860,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2874,7 +2880,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2883,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562094</v>
+        <v>562079</v>
       </c>
       <c r="R22" t="n">
-        <v>7042667</v>
+        <v>7042662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2924,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2928,7 +2934,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2955,10 +2966,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310396</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2966,16 +2977,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2995,10 +3006,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562094</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3040,12 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,38 +3078,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310484</v>
+        <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3112,10 +3117,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562079</v>
+        <v>562035</v>
       </c>
       <c r="R24" t="n">
-        <v>7042662</v>
+        <v>7042727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3147,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3157,12 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,49 +3296,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310333</v>
+        <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562077</v>
+        <v>562045</v>
       </c>
       <c r="R26" t="n">
-        <v>7042695</v>
+        <v>7042732</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3366,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3395,57 +3391,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310210</v>
+        <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>79076</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562045</v>
+        <v>562077</v>
       </c>
       <c r="R27" t="n">
-        <v>7042732</v>
+        <v>7042695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,12 +3502,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129310389</v>
+        <v>129309880</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562065</v>
+        <v>562069</v>
       </c>
       <c r="R2" t="n">
-        <v>7042680</v>
+        <v>7042614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310680</v>
+        <v>129310389</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562140</v>
+        <v>562065</v>
       </c>
       <c r="R3" t="n">
-        <v>7042590</v>
+        <v>7042680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129309880</v>
+        <v>129310680</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562069</v>
+        <v>562140</v>
       </c>
       <c r="R4" t="n">
-        <v>7042614</v>
+        <v>7042590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
         <v>129310232</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>129310242</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129310667</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>129309580</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>129309285</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>129310984</v>
       </c>
       <c r="B10" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129309061</v>
       </c>
       <c r="B11" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>129309685</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>129310513</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129310043</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>129310366</v>
       </c>
       <c r="B15" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129309882</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>129309112</v>
       </c>
       <c r="B17" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>129310631</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>129309443</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129310847</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310662</v>
+        <v>129310396</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,16 +2743,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562130</v>
+        <v>562094</v>
       </c>
       <c r="R21" t="n">
-        <v>7042598</v>
+        <v>7042667</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,12 +2817,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310396</v>
+        <v>129310662</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,16 +2972,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3006,10 +3001,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562094</v>
+        <v>562130</v>
       </c>
       <c r="R23" t="n">
-        <v>7042667</v>
+        <v>7042598</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3041,7 +3036,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3051,7 +3046,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,7 @@
         <v>129310206</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>129310777</v>
       </c>
       <c r="B25" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>129310210</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>129310333</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>129310528</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,32 +3625,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310912</v>
+        <v>129310558</v>
       </c>
       <c r="B29" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562084</v>
+        <v>562100</v>
       </c>
       <c r="R29" t="n">
-        <v>7042525</v>
+        <v>7042638</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,10 +3732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310558</v>
+        <v>129310001</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3767,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562100</v>
+        <v>562049</v>
       </c>
       <c r="R30" t="n">
-        <v>7042638</v>
+        <v>7042649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,32 +3839,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310001</v>
+        <v>129310912</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562049</v>
+        <v>562084</v>
       </c>
       <c r="R31" t="n">
-        <v>7042649</v>
+        <v>7042525</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3949,7 +3949,7 @@
         <v>129309661</v>
       </c>
       <c r="B32" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4053,45 +4053,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129309746</v>
+        <v>129310811</v>
       </c>
       <c r="B33" t="n">
-        <v>79162</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562063</v>
+        <v>562122</v>
       </c>
       <c r="R33" t="n">
-        <v>7042591</v>
+        <v>7042513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4123,7 +4127,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4133,7 +4137,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,61 +4152,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129310811</v>
+        <v>129309746</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>79167</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562122</v>
+        <v>562063</v>
       </c>
       <c r="R34" t="n">
-        <v>7042513</v>
+        <v>7042591</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129310114</v>
+        <v>129309127</v>
       </c>
       <c r="B36" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562088</v>
+        <v>561985</v>
       </c>
       <c r="R36" t="n">
-        <v>7042660</v>
+        <v>7042548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4473,22 +4473,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309127</v>
+        <v>129309754</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561985</v>
+        <v>562081</v>
       </c>
       <c r="R37" t="n">
-        <v>7042548</v>
+        <v>7042603</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129309754</v>
+        <v>129310114</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562081</v>
+        <v>562088</v>
       </c>
       <c r="R38" t="n">
-        <v>7042603</v>
+        <v>7042660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,12 +4687,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129309880</v>
+        <v>129310114</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562069</v>
+        <v>562088</v>
       </c>
       <c r="R2" t="n">
-        <v>7042614</v>
+        <v>7042660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,61 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129310389</v>
+        <v>129310667</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562065</v>
+        <v>562146</v>
       </c>
       <c r="R3" t="n">
-        <v>7042680</v>
+        <v>7042570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,49 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129310680</v>
+        <v>129310777</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562140</v>
+        <v>562125</v>
       </c>
       <c r="R4" t="n">
-        <v>7042590</v>
+        <v>7042515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129310232</v>
+        <v>129309112</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562053</v>
+        <v>561993</v>
       </c>
       <c r="R5" t="n">
-        <v>7042723</v>
+        <v>7042559</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,49 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129310242</v>
+        <v>129309285</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562061</v>
+        <v>562005</v>
       </c>
       <c r="R6" t="n">
-        <v>7042718</v>
+        <v>7042560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129310667</v>
+        <v>129309661</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562146</v>
+        <v>562061</v>
       </c>
       <c r="R7" t="n">
-        <v>7042570</v>
+        <v>7042576</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,22 +1305,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129309580</v>
+        <v>129310912</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562055</v>
+        <v>562084</v>
       </c>
       <c r="R8" t="n">
-        <v>7042557</v>
+        <v>7042525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1413,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129309285</v>
+        <v>129310984</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1475,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562005</v>
+        <v>562038</v>
       </c>
       <c r="R9" t="n">
-        <v>7042560</v>
+        <v>7042536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129310984</v>
+        <v>129309127</v>
       </c>
       <c r="B10" t="n">
-        <v>92875</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1582,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562038</v>
+        <v>561985</v>
       </c>
       <c r="R10" t="n">
-        <v>7042536</v>
+        <v>7042548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1627,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129309061</v>
+        <v>129309443</v>
       </c>
       <c r="B11" t="n">
-        <v>78838</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561977</v>
+        <v>562018</v>
       </c>
       <c r="R11" t="n">
-        <v>7042590</v>
+        <v>7042558</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129309685</v>
+        <v>129309580</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,38 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562066</v>
+        <v>562055</v>
       </c>
       <c r="R12" t="n">
-        <v>7042569</v>
+        <v>7042557</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,14 +1852,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129310513</v>
+        <v>129309754</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1907,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562072</v>
+        <v>562081</v>
       </c>
       <c r="R13" t="n">
-        <v>7042648</v>
+        <v>7042603</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129310043</v>
+        <v>129309882</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,38 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562044</v>
+        <v>562082</v>
       </c>
       <c r="R14" t="n">
-        <v>7042672</v>
+        <v>7042627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,30 +2066,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129310366</v>
+        <v>129310001</v>
       </c>
       <c r="B15" t="n">
-        <v>91613</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2121,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562097</v>
+        <v>562049</v>
       </c>
       <c r="R15" t="n">
-        <v>7042658</v>
+        <v>7042649</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,14 +2173,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129309882</v>
+        <v>129310210</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2228,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562082</v>
+        <v>562045</v>
       </c>
       <c r="R16" t="n">
-        <v>7042627</v>
+        <v>7042732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129309112</v>
+        <v>129310513</v>
       </c>
       <c r="B17" t="n">
-        <v>92875</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561993</v>
+        <v>562072</v>
       </c>
       <c r="R17" t="n">
-        <v>7042559</v>
+        <v>7042648</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,14 +2387,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129310631</v>
+        <v>129310558</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2442,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562130</v>
+        <v>562100</v>
       </c>
       <c r="R18" t="n">
-        <v>7042597</v>
+        <v>7042638</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,14 +2494,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129309443</v>
+        <v>129310631</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2549,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562018</v>
+        <v>562130</v>
       </c>
       <c r="R19" t="n">
-        <v>7042558</v>
+        <v>7042597</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,49 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129310847</v>
+        <v>129309061</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562116</v>
+        <v>561977</v>
       </c>
       <c r="R20" t="n">
-        <v>7042514</v>
+        <v>7042590</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2705,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,22 +2696,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129310396</v>
+        <v>129310044</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,39 +2719,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562094</v>
+        <v>562139</v>
       </c>
       <c r="R21" t="n">
-        <v>7042667</v>
+        <v>7042644</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2817,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2832,22 +2803,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129310484</v>
+        <v>129309746</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,39 +2826,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562079</v>
+        <v>562063</v>
       </c>
       <c r="R22" t="n">
-        <v>7042662</v>
+        <v>7042591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2929,12 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2949,22 +2910,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129310662</v>
+        <v>129310232</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2972,39 +2933,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562130</v>
+        <v>562053</v>
       </c>
       <c r="R23" t="n">
-        <v>7042598</v>
+        <v>7042723</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3036,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3046,12 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,37 +3029,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129310206</v>
+        <v>129310396</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562035</v>
+        <v>562094</v>
       </c>
       <c r="R24" t="n">
-        <v>7042727</v>
+        <v>7042667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3152,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129310777</v>
+        <v>129310352</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,34 +3152,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562125</v>
+        <v>562104</v>
       </c>
       <c r="R25" t="n">
-        <v>7042515</v>
+        <v>7042696</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3226,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,22 +3246,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129310210</v>
+        <v>129310484</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3307,34 +3269,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562045</v>
+        <v>562079</v>
       </c>
       <c r="R26" t="n">
-        <v>7042732</v>
+        <v>7042662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3376,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,37 +3375,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129310333</v>
+        <v>129310662</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>63</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3442,10 +3415,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562077</v>
+        <v>562130</v>
       </c>
       <c r="R27" t="n">
-        <v>7042695</v>
+        <v>7042598</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3450,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3460,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3502,22 +3480,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129310528</v>
+        <v>129309685</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3544,7 +3522,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3553,10 +3531,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562078</v>
+        <v>562066</v>
       </c>
       <c r="R28" t="n">
-        <v>7042633</v>
+        <v>7042569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3566,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,7 +3576,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,45 +3603,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129310558</v>
+        <v>129309880</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562100</v>
+        <v>562069</v>
       </c>
       <c r="R29" t="n">
-        <v>7042638</v>
+        <v>7042614</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3695,7 +3677,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3705,7 +3687,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,45 +3714,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129310001</v>
+        <v>129310043</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562049</v>
+        <v>562044</v>
       </c>
       <c r="R30" t="n">
-        <v>7042649</v>
+        <v>7042672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3788,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3798,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3839,45 +3825,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129310912</v>
+        <v>129310206</v>
       </c>
       <c r="B31" t="n">
-        <v>92875</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562084</v>
+        <v>562035</v>
       </c>
       <c r="R31" t="n">
-        <v>7042525</v>
+        <v>7042727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,7 +3899,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3919,7 +3909,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,35 +3936,39 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129309661</v>
+        <v>129310242</v>
       </c>
       <c r="B32" t="n">
-        <v>92875</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
@@ -3984,7 +3978,7 @@
         <v>562061</v>
       </c>
       <c r="R32" t="n">
-        <v>7042576</v>
+        <v>7042718</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,7 +4010,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4026,7 +4020,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4053,10 +4047,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129310811</v>
+        <v>129310333</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4083,19 +4077,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>63</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562122</v>
+        <v>562077</v>
       </c>
       <c r="R33" t="n">
-        <v>7042513</v>
+        <v>7042695</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4127,7 +4121,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4137,7 +4131,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4152,57 +4146,61 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129309746</v>
+        <v>129310389</v>
       </c>
       <c r="B34" t="n">
-        <v>79167</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562063</v>
+        <v>562065</v>
       </c>
       <c r="R34" t="n">
-        <v>7042591</v>
+        <v>7042680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4234,7 +4232,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4244,7 +4242,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4274,7 +4272,7 @@
         <v>129310519</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,45 +4376,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129309127</v>
+        <v>129310528</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561985</v>
+        <v>562078</v>
       </c>
       <c r="R36" t="n">
-        <v>7042548</v>
+        <v>7042633</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4448,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4458,7 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4485,45 +4487,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129309754</v>
+        <v>129310680</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562081</v>
+        <v>562140</v>
       </c>
       <c r="R37" t="n">
-        <v>7042603</v>
+        <v>7042590</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4555,7 +4561,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4565,7 +4571,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4592,45 +4598,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129310114</v>
+        <v>129310811</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Lungnan, Stor-Lungnan, Ång</t>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562088</v>
+        <v>562122</v>
       </c>
       <c r="R38" t="n">
-        <v>7042660</v>
+        <v>7042513</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,7 +4672,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4672,7 +4682,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,15 +4697,126 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129310847</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bäverhugstret, Bäverhugstret, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>562116</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7042514</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51693-2024 artfynd.xlsx
+++ b/artfynd/A 51693-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310114</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310667</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310777</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309112</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309285</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309661</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310912</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310984</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309127</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309443</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309580</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309754</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309882</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310001</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310210</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310513</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310558</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310631</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309061</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310044</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309746</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310232</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,6 +3253,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310396</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3255,6 +3375,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310352</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3372,6 +3497,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310484</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3489,6 +3619,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310662</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3600,6 +3735,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309685</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3711,6 +3851,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129309880</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3822,6 +3967,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310043</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3933,6 +4083,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310206</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4044,6 +4199,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310242</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4155,6 +4315,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310333</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4266,6 +4431,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310389</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4373,6 +4543,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310519</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4484,6 +4659,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310528</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4595,6 +4775,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310680</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4706,6 +4891,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310811</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4817,8 +5007,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129310847</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>